--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:21</t>
+    <t xml:space="preserve">2026-09-10 01:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:36</t>
+    <t xml:space="preserve">2026-09-18 11:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:32</t>
+    <t xml:space="preserve">2026-09-23 15:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:36</t>
+    <t xml:space="preserve">2026-10-05 16:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -829,7 +829,7 @@
         <v>52.98</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>100.61</v>
+        <v>100.62</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>100.44</v>
@@ -1438,7 +1438,7 @@
         <v>59.78</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>100.5</v>
+        <v>100.51</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>99.34</v>
